--- a/scraper/downloads/yad2_page_4.xlsx
+++ b/scraper/downloads/yad2_page_4.xlsx
@@ -214,9 +214,9 @@
     <col min="11" max="11" width="10.8" customWidth="1"/>
     <col min="12" max="12" width="25.650000000000002" customWidth="1"/>
     <col min="13" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="35.1" customWidth="1"/>
+    <col min="14" max="14" width="54" customWidth="1"/>
     <col min="15" max="15" width="13.5" customWidth="1"/>
-    <col min="16" max="16" width="13.5" customWidth="1"/>
+    <col min="16" max="16" width="51.300000000000004" customWidth="1"/>
     <col min="17" max="17" width="8.100000000000001" customWidth="1"/>
     <col min="18" max="18" width="6.75" customWidth="1"/>
     <col min="19" max="19" width="40.5" customWidth="1"/>
@@ -337,46 +337,58 @@
         </is>
       </c>
       <c r="D3" s="65">
-        <v>184</v>
-      </c>
-      <c r="E3" s="65">
-        <v>8</v>
+        <v>180</v>
+      </c>
+      <c t="inlineStr" r="E3">
+        <is>
+          <t xml:space="preserve">/1313</t>
+        </is>
       </c>
       <c t="inlineStr" r="F3">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c r="G3" s="65">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">44.8מ״ר</t>
+          <t xml:space="preserve">187מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I3">
         <is>
-          <t xml:space="preserve">מרפסת: 1.1מ״ר</t>
+          <t xml:space="preserve">מרפסת: 7.42מ״רמרפסת: 8.27מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J3">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">2חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K3">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L3">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
         </is>
       </c>
       <c t="inlineStr" r="N3">
         <is>
-          <t xml:space="preserve">קולטון מוישי</t>
-        </is>
-      </c>
-      <c r="O3" s="65">
-        <v>0</v>
+          <t xml:space="preserve">משה בר עמי(054) 220-5522בועז הר עמי(054) 770-3070</t>
+        </is>
+      </c>
+      <c r="O3" s="63">
+        <v>18500000</v>
+      </c>
+      <c t="inlineStr" r="P3">
+        <is>
+          <t xml:space="preserve">מיזוגמעליתממ״דאלחנןגישה לנכיםבניין חדש</t>
+        </is>
       </c>
       <c t="inlineStr" r="R3">
         <is>
@@ -385,7 +397,7 @@
       </c>
       <c t="inlineStr" r="S3">
         <is>
-          <t xml:space="preserve">משה קולטון04-11-2024</t>
+          <t xml:space="preserve">אלחנן רווח16-07-2024</t>
         </is>
       </c>
     </row>
@@ -404,10 +416,10 @@
         </is>
       </c>
       <c r="D4" s="65">
-        <v>60</v>
+        <v>184</v>
       </c>
       <c r="E4" s="65">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c t="inlineStr" r="F4">
         <is>
@@ -415,11 +427,16 @@
         </is>
       </c>
       <c r="G4" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">87מ״ר</t>
+          <t xml:space="preserve">44.8מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I4">
+        <is>
+          <t xml:space="preserve">מרפסת: 1.1מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
@@ -434,7 +451,7 @@
       </c>
       <c t="inlineStr" r="N4">
         <is>
-          <t xml:space="preserve">יהודה סרגה(058) 749-8760</t>
+          <t xml:space="preserve">קולטון מוישי</t>
         </is>
       </c>
       <c r="O4" s="65">
@@ -447,7 +464,7 @@
       </c>
       <c t="inlineStr" r="S4">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">משה קולטון04-11-2024</t>
         </is>
       </c>
     </row>
@@ -462,33 +479,26 @@
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">יצחק בראשי</t>
+          <t xml:space="preserve">יפו</t>
         </is>
       </c>
       <c r="D5" s="65">
-        <v>30</v>
-      </c>
-      <c t="inlineStr" r="E5">
-        <is>
-          <t xml:space="preserve">/32</t>
-        </is>
+        <v>60</v>
+      </c>
+      <c r="E5" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F5">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="n" r="G5">
-        <v>3.5</v>
+      <c r="G5" s="65">
+        <v>3</v>
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">105מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I5">
-        <is>
-          <t xml:space="preserve">מרפסת: 20.9מ״ר</t>
+          <t xml:space="preserve">87מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J5">
@@ -501,18 +511,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L5">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N5">
         <is>
-          <t xml:space="preserve">דני עמדי(054) 249-9615</t>
-        </is>
-      </c>
-      <c r="O5" s="63">
-        <v>5000000</v>
+          <t xml:space="preserve">יהודה סרגה(058) 749-8760</t>
+        </is>
+      </c>
+      <c r="O5" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R5">
         <is>
@@ -521,7 +526,7 @@
       </c>
       <c t="inlineStr" r="S5">
         <is>
-          <t xml:space="preserve">אריה טאו17-05-2026</t>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -536,31 +541,33 @@
       </c>
       <c t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">ישמח מלך</t>
+          <t xml:space="preserve">יצחק בראשי</t>
         </is>
       </c>
       <c r="D6" s="65">
-        <v>0</v>
-      </c>
-      <c r="E6" s="65">
-        <v>3</v>
+        <v>30</v>
+      </c>
+      <c t="inlineStr" r="E6">
+        <is>
+          <t xml:space="preserve">/32</t>
+        </is>
       </c>
       <c t="inlineStr" r="F6">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c r="G6" s="65">
-        <v>4</v>
+      <c t="n" r="G6">
+        <v>3.5</v>
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">250מ״ר</t>
+          <t xml:space="preserve">105מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I6">
         <is>
-          <t xml:space="preserve">מרפסת: 70מ״ר</t>
+          <t xml:space="preserve">מרפסת: 20.9מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J6">
@@ -573,13 +580,18 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L6">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N6">
         <is>
-          <t xml:space="preserve">לוסקי אלכס(054) 202-0446</t>
-        </is>
-      </c>
-      <c r="O6" s="65">
-        <v>0</v>
+          <t xml:space="preserve">דני עמדי(054) 249-9615</t>
+        </is>
+      </c>
+      <c r="O6" s="63">
+        <v>5000000</v>
       </c>
       <c t="inlineStr" r="R6">
         <is>
@@ -588,7 +600,7 @@
       </c>
       <c t="inlineStr" r="S6">
         <is>
-          <t xml:space="preserve">אורן כהן04-11-2024</t>
+          <t xml:space="preserve">אריה טאו17-05-2026</t>
         </is>
       </c>
     </row>
@@ -607,10 +619,10 @@
         </is>
       </c>
       <c r="D7" s="65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7" s="65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F7">
         <is>
@@ -622,7 +634,12 @@
       </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">189מ״ר</t>
+          <t xml:space="preserve">250מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I7">
+        <is>
+          <t xml:space="preserve">מרפסת: 70מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J7">
@@ -637,7 +654,7 @@
       </c>
       <c t="inlineStr" r="N7">
         <is>
-          <t xml:space="preserve">חולוב אסף</t>
+          <t xml:space="preserve">לוסקי אלכס(054) 202-0446</t>
         </is>
       </c>
       <c r="O7" s="65">
@@ -665,31 +682,26 @@
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">ישראליס</t>
+          <t xml:space="preserve">ישמח מלך</t>
         </is>
       </c>
       <c r="D8" s="65">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E8" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">בית פרטי</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G8" s="65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t xml:space="preserve">305מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I8">
-        <is>
-          <t xml:space="preserve">מרפסת: 220מ״ר</t>
+          <t xml:space="preserve">189מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J8">
@@ -702,18 +714,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L8">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N8">
         <is>
-          <t xml:space="preserve">דניאל(05) 569-לא בשוק</t>
-        </is>
-      </c>
-      <c r="O8" s="63">
-        <v>47000000</v>
+          <t xml:space="preserve">חולוב אסף</t>
+        </is>
+      </c>
+      <c r="O8" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R8">
         <is>
@@ -722,7 +729,7 @@
       </c>
       <c t="inlineStr" r="S8">
         <is>
-          <t xml:space="preserve">אורן כהן19-03-2026</t>
+          <t xml:space="preserve">אורן כהן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -737,18 +744,18 @@
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">כהנוב</t>
+          <t xml:space="preserve">ישראליס</t>
         </is>
       </c>
       <c r="D9" s="65">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E9" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F9">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">בית פרטי</t>
         </is>
       </c>
       <c r="G9" s="65">
@@ -756,7 +763,12 @@
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">0מ״ר</t>
+          <t xml:space="preserve">305מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I9">
+        <is>
+          <t xml:space="preserve">מרפסת: 220מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J9">
@@ -769,13 +781,18 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L9">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N9">
         <is>
-          <t xml:space="preserve">אורן אצל</t>
-        </is>
-      </c>
-      <c r="O9" s="65">
-        <v>0</v>
+          <t xml:space="preserve">דניאל(05) 569-לא בשוק</t>
+        </is>
+      </c>
+      <c r="O9" s="63">
+        <v>47000000</v>
       </c>
       <c t="inlineStr" r="R9">
         <is>
@@ -784,7 +801,7 @@
       </c>
       <c t="inlineStr" r="S9">
         <is>
-          <t xml:space="preserve">אורן כהן04-11-2024</t>
+          <t xml:space="preserve">אורן כהן19-03-2026</t>
         </is>
       </c>
     </row>
@@ -799,7 +816,7 @@
       </c>
       <c t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">כובשי קטמון</t>
+          <t xml:space="preserve">כהנוב</t>
         </is>
       </c>
       <c r="D10" s="65">
@@ -810,15 +827,15 @@
       </c>
       <c t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">דירת גן</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G10" s="65">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">78מ״ר</t>
+          <t xml:space="preserve">0מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J10">
@@ -831,28 +848,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L10">
-        <is>
-          <t xml:space="preserve">צפון דרום מערב</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M10">
-        <is>
-          <t xml:space="preserve">עורף</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N10">
         <is>
-          <t xml:space="preserve">אלון ינאי(054) 446-5951</t>
-        </is>
-      </c>
-      <c r="O10" s="63">
-        <v>3600000</v>
-      </c>
-      <c t="inlineStr" r="P10">
-        <is>
-          <t xml:space="preserve">גישה לנכים</t>
-        </is>
+          <t xml:space="preserve">אורן אצל</t>
+        </is>
+      </c>
+      <c r="O10" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R10">
         <is>
@@ -861,7 +863,7 @@
       </c>
       <c t="inlineStr" r="S10">
         <is>
-          <t xml:space="preserve">מיכאל בלוך01-07-2024</t>
+          <t xml:space="preserve">אורן כהן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -876,7 +878,7 @@
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">כספי</t>
+          <t xml:space="preserve">כובשי קטמון</t>
         </is>
       </c>
       <c r="D11" s="65">
@@ -887,7 +889,7 @@
       </c>
       <c t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">דירת גן</t>
         </is>
       </c>
       <c r="G11" s="65">
@@ -895,36 +897,41 @@
       </c>
       <c t="inlineStr" r="H11">
         <is>
-          <t xml:space="preserve">174מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I11">
-        <is>
-          <t xml:space="preserve">מרפסת: 45מ״רמרפסת: 45מ״רמרפסת: 70מ״ר</t>
+          <t xml:space="preserve">78מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J11">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K11">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="L11">
         <is>
-          <t xml:space="preserve">צפון דרום</t>
+          <t xml:space="preserve">צפון דרום מערב</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M11">
+        <is>
+          <t xml:space="preserve">עורף</t>
         </is>
       </c>
       <c t="inlineStr" r="N11">
         <is>
-          <t xml:space="preserve">יהודה סרגה(058) 749-8760</t>
+          <t xml:space="preserve">אלון ינאי(054) 446-5951</t>
         </is>
       </c>
       <c r="O11" s="63">
-        <v>9250000</v>
+        <v>3600000</v>
+      </c>
+      <c t="inlineStr" r="P11">
+        <is>
+          <t xml:space="preserve">גישה לנכים</t>
+        </is>
       </c>
       <c t="inlineStr" r="R11">
         <is>
@@ -933,7 +940,7 @@
       </c>
       <c t="inlineStr" r="S11">
         <is>
-          <t xml:space="preserve">רבקה בן זקן06-01-2025</t>
+          <t xml:space="preserve">מיכאל בלוך01-07-2024</t>
         </is>
       </c>
     </row>
@@ -948,14 +955,14 @@
       </c>
       <c t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">ללא רחוב</t>
+          <t xml:space="preserve">כספי</t>
         </is>
       </c>
       <c r="D12" s="65">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E12" s="65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F12">
         <is>
@@ -963,30 +970,40 @@
         </is>
       </c>
       <c r="G12" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H12">
         <is>
-          <t xml:space="preserve">75מ״ר</t>
+          <t xml:space="preserve">174מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I12">
+        <is>
+          <t xml:space="preserve">מרפסת: 45מ״רמרפסת: 45מ״רמרפסת: 70מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J12">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K12">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L12">
+        <is>
+          <t xml:space="preserve">צפון דרום</t>
         </is>
       </c>
       <c t="inlineStr" r="N12">
         <is>
-          <t xml:space="preserve">מרים(052) 350-4573</t>
-        </is>
-      </c>
-      <c r="O12" s="65">
-        <v>0</v>
+          <t xml:space="preserve">יהודה סרגה(058) 749-8760</t>
+        </is>
+      </c>
+      <c r="O12" s="63">
+        <v>9250000</v>
       </c>
       <c t="inlineStr" r="R12">
         <is>
@@ -995,7 +1012,7 @@
       </c>
       <c t="inlineStr" r="S12">
         <is>
-          <t xml:space="preserve">מירי רענן04-11-2024</t>
+          <t xml:space="preserve">רבקה בן זקן06-01-2025</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="F13">
         <is>
@@ -1025,11 +1042,11 @@
         </is>
       </c>
       <c r="G13" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">93מ״ר</t>
+          <t xml:space="preserve">75מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J13">
@@ -1044,7 +1061,7 @@
       </c>
       <c t="inlineStr" r="N13">
         <is>
-          <t xml:space="preserve">יהודה סרגה</t>
+          <t xml:space="preserve">מרים(052) 350-4573</t>
         </is>
       </c>
       <c r="O13" s="65">
@@ -1057,7 +1074,7 @@
       </c>
       <c t="inlineStr" r="S13">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">מירי רענן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1087,11 +1104,11 @@
         </is>
       </c>
       <c r="G14" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t xml:space="preserve">128מ״ר</t>
+          <t xml:space="preserve">93מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J14">
@@ -1106,7 +1123,7 @@
       </c>
       <c t="inlineStr" r="N14">
         <is>
-          <t xml:space="preserve">ישי דוד(050) 476-3062</t>
+          <t xml:space="preserve">יהודה סרגה</t>
         </is>
       </c>
       <c r="O14" s="65">
@@ -1134,7 +1151,7 @@
       </c>
       <c t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">מאיר שחם</t>
+          <t xml:space="preserve">ללא רחוב</t>
         </is>
       </c>
       <c r="D15" s="65">
@@ -1149,11 +1166,11 @@
         </is>
       </c>
       <c r="G15" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H15">
         <is>
-          <t xml:space="preserve">62.5מ״ר</t>
+          <t xml:space="preserve">128מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J15">
@@ -1168,7 +1185,7 @@
       </c>
       <c t="inlineStr" r="N15">
         <is>
-          <t xml:space="preserve">יהודה סרגה</t>
+          <t xml:space="preserve">ישי דוד(050) 476-3062</t>
         </is>
       </c>
       <c r="O15" s="65">
@@ -1215,7 +1232,7 @@
       </c>
       <c t="inlineStr" r="H16">
         <is>
-          <t xml:space="preserve">70מ״ר</t>
+          <t xml:space="preserve">62.5מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J16">
@@ -1273,11 +1290,11 @@
         </is>
       </c>
       <c r="G17" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="H17">
         <is>
-          <t xml:space="preserve">163מ״ר</t>
+          <t xml:space="preserve">70מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J17">
@@ -1324,10 +1341,10 @@
         </is>
       </c>
       <c r="D18" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="65">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F18">
         <is>
@@ -1335,35 +1352,30 @@
         </is>
       </c>
       <c r="G18" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H18">
         <is>
-          <t xml:space="preserve">93מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I18">
-        <is>
-          <t xml:space="preserve">מרפסת: 12מ״ר</t>
+          <t xml:space="preserve">163מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J18">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K18">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N18">
         <is>
-          <t xml:space="preserve">יהודה סרגה(058) 749-8760</t>
-        </is>
-      </c>
-      <c r="O18" s="63">
-        <v>8500000</v>
+          <t xml:space="preserve">יהודה סרגה</t>
+        </is>
+      </c>
+      <c r="O18" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R18">
         <is>
@@ -1372,7 +1384,7 @@
       </c>
       <c t="inlineStr" r="S18">
         <is>
-          <t xml:space="preserve">רבקה בן זקן08-01-2025</t>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1403,10 @@
         </is>
       </c>
       <c r="D19" s="65">
-        <v>2</v>
-      </c>
-      <c t="inlineStr" r="E19">
-        <is>
-          <t xml:space="preserve">/2519</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E19" s="65">
+        <v>7</v>
       </c>
       <c t="inlineStr" r="F19">
         <is>
@@ -1408,12 +1418,12 @@
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">69מ״ר</t>
+          <t xml:space="preserve">93מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I19">
         <is>
-          <t xml:space="preserve">מרפסת: 10מ״ר</t>
+          <t xml:space="preserve">מרפסת: 12מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J19">
@@ -1423,21 +1433,16 @@
       </c>
       <c t="inlineStr" r="K19">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="L19">
-        <is>
-          <t xml:space="preserve">דרום מערב</t>
+          <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N19">
         <is>
-          <t xml:space="preserve">שי לוי(050) 432-0555</t>
+          <t xml:space="preserve">יהודה סרגה(058) 749-8760</t>
         </is>
       </c>
       <c r="O19" s="63">
-        <v>7200000</v>
+        <v>8500000</v>
       </c>
       <c t="inlineStr" r="R19">
         <is>
@@ -1446,7 +1451,7 @@
       </c>
       <c t="inlineStr" r="S19">
         <is>
-          <t xml:space="preserve">אורן כהן21-08-2024</t>
+          <t xml:space="preserve">רבקה בן זקן08-01-2025</t>
         </is>
       </c>
     </row>
@@ -1465,29 +1470,29 @@
         </is>
       </c>
       <c r="D20" s="65">
+        <v>2</v>
+      </c>
+      <c t="inlineStr" r="E20">
+        <is>
+          <t xml:space="preserve">/2519</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="F20">
+        <is>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c r="G20" s="65">
         <v>3</v>
       </c>
-      <c t="inlineStr" r="E20">
-        <is>
-          <t xml:space="preserve">/283</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="F20">
-        <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c r="G20" s="65">
-        <v>0</v>
-      </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t xml:space="preserve">92מ״ר</t>
+          <t xml:space="preserve">69מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I20">
         <is>
-          <t xml:space="preserve">מרפסת: 12מ״רמרפסת: 1מ״רמרפסת: 1מ״ר</t>
+          <t xml:space="preserve">מרפסת: 10מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J20">
@@ -1497,21 +1502,21 @@
       </c>
       <c t="inlineStr" r="K20">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="L20">
         <is>
-          <t xml:space="preserve">צפון מערב</t>
+          <t xml:space="preserve">דרום מערב</t>
         </is>
       </c>
       <c t="inlineStr" r="N20">
         <is>
-          <t xml:space="preserve">פבריציו סרבי(054) 999-0792</t>
+          <t xml:space="preserve">שי לוי(050) 432-0555</t>
         </is>
       </c>
       <c r="O20" s="63">
-        <v>7350000</v>
+        <v>7200000</v>
       </c>
       <c t="inlineStr" r="R20">
         <is>
@@ -1520,7 +1525,7 @@
       </c>
       <c t="inlineStr" r="S20">
         <is>
-          <t xml:space="preserve">אריה טאו11-02-2026</t>
+          <t xml:space="preserve">אורן כהן21-08-2024</t>
         </is>
       </c>
     </row>
@@ -1535,15 +1540,15 @@
       </c>
       <c t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">מאיר שכם</t>
+          <t xml:space="preserve">מאיר שחם</t>
         </is>
       </c>
       <c r="D21" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="E21">
         <is>
-          <t xml:space="preserve">/101</t>
+          <t xml:space="preserve">/283</t>
         </is>
       </c>
       <c t="inlineStr" r="F21">
@@ -1556,12 +1561,17 @@
       </c>
       <c t="inlineStr" r="H21">
         <is>
-          <t xml:space="preserve">83מ״ר</t>
+          <t xml:space="preserve">92מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I21">
+        <is>
+          <t xml:space="preserve">מרפסת: 12מ״רמרפסת: 1מ״רמרפסת: 1מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J21">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K21">
@@ -1569,8 +1579,18 @@
           <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L21">
+        <is>
+          <t xml:space="preserve">צפון מערב</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="N21">
+        <is>
+          <t xml:space="preserve">פבריציו סרבי(054) 999-0792</t>
+        </is>
+      </c>
       <c r="O21" s="63">
-        <v>4750000</v>
+        <v>7350000</v>
       </c>
       <c t="inlineStr" r="R21">
         <is>
@@ -1579,7 +1599,7 @@
       </c>
       <c t="inlineStr" r="S21">
         <is>
-          <t xml:space="preserve">דוב רבינובץ\'04-06-2026</t>
+          <t xml:space="preserve">אריה טאו11-02-2026</t>
         </is>
       </c>
     </row>
@@ -1600,8 +1620,10 @@
       <c r="D22" s="65">
         <v>2</v>
       </c>
-      <c r="E22" s="65">
-        <v>0</v>
+      <c t="inlineStr" r="E22">
+        <is>
+          <t xml:space="preserve">/101</t>
+        </is>
       </c>
       <c t="inlineStr" r="F22">
         <is>
@@ -1613,12 +1635,12 @@
       </c>
       <c t="inlineStr" r="H22">
         <is>
-          <t xml:space="preserve">78מ״ר</t>
+          <t xml:space="preserve">83מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J22">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K22">
@@ -1627,7 +1649,7 @@
         </is>
       </c>
       <c r="O22" s="63">
-        <v>4500000</v>
+        <v>4750000</v>
       </c>
       <c t="inlineStr" r="R22">
         <is>
@@ -1651,52 +1673,40 @@
       </c>
       <c t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">מטודלה</t>
+          <t xml:space="preserve">מאיר שכם</t>
         </is>
       </c>
       <c r="D23" s="65">
-        <v>34</v>
-      </c>
-      <c t="inlineStr" r="E23">
-        <is>
-          <t xml:space="preserve">/33</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="E23" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G23" s="65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t xml:space="preserve">130מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I23">
-        <is>
-          <t xml:space="preserve">מרפסת: 6מ״רמרפסת: 4מ״ר</t>
+          <t xml:space="preserve">78מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J23">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K23">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="N23">
-        <is>
-          <t xml:space="preserve">ישי רוזנטל (054) 345-3830</t>
+          <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
       <c r="O23" s="63">
-        <v>6500000</v>
+        <v>4500000</v>
       </c>
       <c t="inlineStr" r="R23">
         <is>
@@ -1705,7 +1715,7 @@
       </c>
       <c t="inlineStr" r="S23">
         <is>
-          <t xml:space="preserve">אלחנן רווח08-09-2024</t>
+          <t xml:space="preserve">דוב רבינובץ\'04-06-2026</t>
         </is>
       </c>
     </row>
@@ -1720,57 +1730,52 @@
       </c>
       <c t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">מלכי ישראל</t>
+          <t xml:space="preserve">מטודלה</t>
         </is>
       </c>
       <c r="D24" s="65">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c t="inlineStr" r="E24">
         <is>
-          <t xml:space="preserve">/87</t>
+          <t xml:space="preserve">/33</t>
         </is>
       </c>
       <c t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c r="G24" s="65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">163מ״ר</t>
+          <t xml:space="preserve">130מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
         <is>
-          <t xml:space="preserve">מרפסת: 14מ״ר</t>
+          <t xml:space="preserve">מרפסת: 6מ״רמרפסת: 4מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J24">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K24">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="L24">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N24">
         <is>
-          <t xml:space="preserve">בירנבאום19175603460</t>
+          <t xml:space="preserve">ישי רוזנטל (054) 345-3830</t>
         </is>
       </c>
       <c r="O24" s="63">
-        <v>12500000</v>
+        <v>6500000</v>
       </c>
       <c t="inlineStr" r="R24">
         <is>
@@ -1779,7 +1784,7 @@
       </c>
       <c t="inlineStr" r="S24">
         <is>
-          <t xml:space="preserve">אין שיוך לאיש מכירות05-06-2024</t>
+          <t xml:space="preserve">אלחנן רווח08-09-2024</t>
         </is>
       </c>
     </row>
@@ -1794,33 +1799,33 @@
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">מעבר המתלה</t>
+          <t xml:space="preserve">מלכי ישראל</t>
         </is>
       </c>
       <c r="D25" s="65">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c t="inlineStr" r="E25">
         <is>
-          <t xml:space="preserve">/77</t>
+          <t xml:space="preserve">/87</t>
         </is>
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G25" s="65">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">211מ״ר</t>
+          <t xml:space="preserve">163מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I25">
         <is>
-          <t xml:space="preserve">מרפסת: 44מ״ר</t>
+          <t xml:space="preserve">מרפסת: 14מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J25">
@@ -1833,13 +1838,18 @@
           <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L25">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N25">
         <is>
-          <t xml:space="preserve">קפיטל גולד(054) 621-7117</t>
+          <t xml:space="preserve">בירנבאום19175603460</t>
         </is>
       </c>
       <c r="O25" s="63">
-        <v>13830762</v>
+        <v>12500000</v>
       </c>
       <c t="inlineStr" r="R25">
         <is>
@@ -1848,7 +1858,7 @@
       </c>
       <c t="inlineStr" r="S25">
         <is>
-          <t xml:space="preserve">רבקה בן זקן13-10-2024</t>
+          <t xml:space="preserve">אין שיוך לאיש מכירות05-06-2024</t>
         </is>
       </c>
     </row>
@@ -1867,24 +1877,29 @@
         </is>
       </c>
       <c r="D26" s="65">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t xml:space="preserve">/42</t>
+          <t xml:space="preserve">/77</t>
         </is>
       </c>
       <c t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c t="n" r="G26">
-        <v>3.5</v>
+          <t xml:space="preserve">פנטהאוז</t>
+        </is>
+      </c>
+      <c r="G26" s="65">
+        <v>7</v>
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">73מ״ר</t>
+          <t xml:space="preserve">211מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I26">
+        <is>
+          <t xml:space="preserve">מרפסת: 44מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J26">
@@ -1894,16 +1909,16 @@
       </c>
       <c t="inlineStr" r="K26">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N26">
         <is>
-          <t xml:space="preserve">מרים חסיד(052) 350-4573</t>
+          <t xml:space="preserve">קפיטל גולד(054) 621-7117</t>
         </is>
       </c>
       <c r="O26" s="63">
-        <v>4000000</v>
+        <v>13830762</v>
       </c>
       <c t="inlineStr" r="R26">
         <is>
@@ -1912,7 +1927,7 @@
       </c>
       <c t="inlineStr" r="S26">
         <is>
-          <t xml:space="preserve">מירי רענן28-10-2024</t>
+          <t xml:space="preserve">רבקה בן זקן13-10-2024</t>
         </is>
       </c>
     </row>
@@ -1927,38 +1942,33 @@
       </c>
       <c t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">משמר העם</t>
+          <t xml:space="preserve">מעבר המתלה</t>
         </is>
       </c>
       <c r="D27" s="65">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t xml:space="preserve">/32</t>
+          <t xml:space="preserve">/42</t>
         </is>
       </c>
       <c t="inlineStr" r="F27">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
-        </is>
-      </c>
-      <c r="G27" s="65">
-        <v>0</v>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c t="n" r="G27">
+        <v>3.5</v>
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t xml:space="preserve">346מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I27">
-        <is>
-          <t xml:space="preserve">מרפסת: 45מ״רגינה: 74מ״ר</t>
+          <t xml:space="preserve">73מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J27">
         <is>
-          <t xml:space="preserve">2חניות</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K27">
@@ -1966,17 +1976,22 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="N27">
+        <is>
+          <t xml:space="preserve">מרים חסיד(052) 350-4573</t>
+        </is>
+      </c>
       <c r="O27" s="63">
-        <v>26500000</v>
+        <v>4000000</v>
       </c>
       <c t="inlineStr" r="R27">
         <is>
-          <t xml:space="preserve">הרשמה</t>
+          <t xml:space="preserve">פעיל</t>
         </is>
       </c>
       <c t="inlineStr" r="S27">
         <is>
-          <t xml:space="preserve">אורן כהן05-08-2024</t>
+          <t xml:space="preserve">מירי רענן28-10-2024</t>
         </is>
       </c>
     </row>
